--- a/docs/moc/Impala - MoC Workshop Interno 21-oct - Preguntas.xlsx
+++ b/docs/moc/Impala - MoC Workshop Interno 21-oct - Preguntas.xlsx
@@ -180,8 +180,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Preguntas" displayName="Preguntas" ref="A1:M24" headerRowCount="1">
-  <autoFilter ref="A1:M24"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Preguntas" displayName="Preguntas" ref="A1:M30" headerRowCount="1">
+  <autoFilter ref="A1:M30"/>
   <tableColumns count="13">
     <tableColumn id="1" name="#"/>
     <tableColumn id="2" name="Bloque"/>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -499,66 +499,73 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Workshop interno MoC (21-oct-2026): preguntas abiertas</t>
+          <t>Workshop interno MoC (21-oct-2026): preguntas abiertas - estado tras la sesión del 21-oct</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Columnas Respuesta / Estado rellenadas con la transcripción del 21-oct. Preguntas 24-29 = nuevas, surgidas en la sesión.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Objetivo: cerrar QUÉ queremos (Shaun: primero el qué, luego cómo lo adapta Intelex). Lo que manda es 'MOC Proposal.xlsx' (Sam).</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Prioridad A = bloquea el diseño para el workshop con Intelex del 27-oct (cerrar mañana sí o sí).</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Prioridad A = bloquea el diseño para el workshop con Intelex del 27-oct (cerrar mañana sí o sí).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Prioridad B = necesaria antes de firmar el workbook.  Prioridad C = rápida / puede decidirla el BA.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Origen: SAM = fichero MOC Proposal; 20-oct = pre-design interno; 19-oct = App Overview con Intelex; BRD = BO-61 v2.0 B.3;</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Origen: SAM = fichero MOC Proposal; 20-oct = pre-design interno; 19-oct = App Overview con Intelex; BRD = BO-61 v2.0 B.3;</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Propuesta BA = idea de Rodrigo / Claude que nadie pidió: presentarla como propuesta, no como requisito.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Durante la reunión: rellenar 'Respuesta / decisión', 'Responsable' y 'Estado'. Después se actualiza el workbook v1.2.</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>Durante la reunión: rellenar 'Respuesta / decisión', 'Responsable' y 'Estado'. Después se actualiza el workbook v1.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Orden sugerido: A (aprobaciones, clasificación, workflow, tareas vs acciones, roles) → B → C.</t>
         </is>
@@ -575,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -709,11 +716,19 @@
           <t>Sin esto no se pueden configurar las aprobaciones automáticas (el núcleo del MoC).</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Local → Regional → Global en un Major (Sam 8:31).</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Decidida</t>
         </is>
       </c>
     </row>
@@ -766,11 +781,19 @@
           <t>Si no se define, Intelex configurará 1 aprobador por nivel y puede no cumplir el procedimiento.</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Local = revisión funcional (Operaciones/Mantenimiento) + firma final del TM: nunca una sola persona (Shaun 4:12 y 5:22, Khesar 10:18). Regional y Global = HSEC + Operaciones. La regla exacta va en el mapa por etapa de Sam.</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Parcial</t>
         </is>
       </c>
     </row>
@@ -823,11 +846,19 @@
           <t>Es el punto con más riesgo de coste (Change Order).</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Imprescindible y AUTOMÁTICO: cuando el TM aprueba, el sistema lanza el siguiente nivel (Sam 10:51).</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Intelex</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Para Intelex</t>
         </is>
       </c>
     </row>
@@ -880,11 +911,19 @@
           <t>Bajo: viene de serie.</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>Sí. Se conservan los tipos de aprobación para añadir aprobaciones funcionales (Sam 8:31).</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Decidida</t>
         </is>
       </c>
     </row>
@@ -937,7 +976,11 @@
           <t>Medio: experiencia de usuario y retrabajo.</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>No se trató el 21-oct.</t>
+        </is>
+      </c>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
@@ -994,11 +1037,19 @@
           <t>Sin la versión final no se pueden cargar las guías de grado en Intelex.</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Change Impact vinculado a la categoría (tipo de cambio). La matriz incluye el grado de cambio y el de peligro. En revisión del equipo. Stylianos no se trató.</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Parcial</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1102,11 @@
           <t>Define la pantalla de Initiation.</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>No se trató el 21-oct.</t>
+        </is>
+      </c>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
@@ -1108,7 +1163,11 @@
           <t>Bajo: es texto de ayuda.</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>No se trató el 21-oct.</t>
+        </is>
+      </c>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
@@ -1165,11 +1224,19 @@
           <t>Todo el workbook depende de esto.</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="2" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Confirmado (Shaun 36:55: 'the workflow looks good'). Una sola aprobación principal antes de Implementation.</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Shaun</t>
+        </is>
+      </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Decidida</t>
         </is>
       </c>
     </row>
@@ -1222,8 +1289,16 @@
           <t>Si se elimina sin decidir, puede que luego haga falta un workflow nuevo (Change Order).</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Sigue abierto (Sam 2:36: 'we can come back to that').</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Sam / Rodrigo</t>
+        </is>
+      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Abierta</t>
@@ -1279,7 +1354,11 @@
           <t>Medio.</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>No se trató el 21-oct.</t>
+        </is>
+      </c>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
@@ -1336,11 +1415,19 @@
           <t>Sin plazos no hay control de MOCs atascados.</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Evaluation/D&amp;A sin plazo (depende del proyecto). Approval: 7 días (Sam 44:08).</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Decidida</t>
         </is>
       </c>
     </row>
@@ -1393,11 +1480,19 @@
           <t>Riesgo de MOCs aprobados sin evaluación.</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Debe ser imposible avanzar sin responder las preguntas (Sam 34:47). Nuevo: las tareas llevan una etapa límite para no bloquear con tareas posteriores.</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Intelex</t>
+        </is>
+      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Decidida</t>
         </is>
       </c>
     </row>
@@ -1450,8 +1545,16 @@
           <t>Medio: carga de datos.</t>
         </is>
       </c>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Abierta: ¿checklist estándar o preguntas según el tipo de cambio? El equipo debe pensarlo (Sam 46:10).</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
           <t>Abierta</t>
@@ -1507,7 +1610,11 @@
           <t>Bajo.</t>
         </is>
       </c>
-      <c r="K16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>No se trató el 21-oct.</t>
+        </is>
+      </c>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
@@ -1564,7 +1671,11 @@
           <t>Bajo.</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>No se trató el 21-oct.</t>
+        </is>
+      </c>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
@@ -1621,11 +1732,19 @@
           <t>Riesgo de duplicar mecanismos y confundir a los usuarios.</t>
         </is>
       </c>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="2" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>Se mantienen las Tasks (Shaun 14:23). Sam prefería acciones pero acepta. El vínculo con Action Plans es opcional: preguntar a Intelex el esfuerzo.</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Shaun</t>
+        </is>
+      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Decidida</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1797,11 @@
           <t>Bloquea la creación de MOCs.</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>No se trató el 21-oct.</t>
+        </is>
+      </c>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
@@ -1735,7 +1858,11 @@
           <t>Bloquea la configuración.</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>No se trató el 21-oct.</t>
+        </is>
+      </c>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
@@ -1792,11 +1919,19 @@
           <t>Sin esto, los temporales caducan sin aviso.</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Approvals a 7 días; Sam: la funcionalidad existe, solo hay que decirles qué queremos. El resto de escalados está pendiente.</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Parcial</t>
         </is>
       </c>
     </row>
@@ -1849,7 +1984,11 @@
           <t>Bajo.</t>
         </is>
       </c>
-      <c r="K22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>No se trató el 21-oct.</t>
+        </is>
+      </c>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr">
         <is>
@@ -1906,7 +2045,11 @@
           <t>Bajo.</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>No se trató el 21-oct.</t>
+        </is>
+      </c>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr">
         <is>
@@ -1963,9 +2106,359 @@
           <t>Si no entran, el BRD queda sin cubrir en esos puntos.</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>'Reason for Change &amp; Technical Basis' aceptado (Khesar 37:51). El resto no se trató.</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
       <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>C. Workflow</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>¿Mantenemos 'Installation Complete?' e 'Installation Confirmed?', o solo uno?</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Do we keep both 'Installation Complete?' and 'Installation Confirmed?' or only one?</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Sam dudó de que hagan falta los dos. Simplifica la etapa Implementation.</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>21-oct, Sam (20:58).</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>21-oct</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Propuesta: quedarse con 'Installation Confirmed?'.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Bajo.</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>C. Workflow</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué preguntas del formulario de auditoría MOC añadimos a Follow Up?</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Which MOC audit form questions do we add to Follow Up?</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Sam propuso reutilizar el formulario de auditoría para cubrir también ese requisito (BRD FR-B3-020).</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>21-oct, Sam (35:00).</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>21-oct</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Sam envía la lista.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Medio: campos de Follow Up.</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>C. Workflow</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>¿Hace falta una aprobación local antes de Start Up (además de la aprobación principal)?</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Do we need an optional local approval before Start Up, on top of the main approval?</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>La aprobación principal es antes de Implementation. Shaun: lo previo al arranque se hace en local. Hay que saber si esa firma local se registra como aprobación o basta con las tareas PSSR.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>21-oct, Sam (21:23) y Shaun (25:35).</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>21-oct</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Opción 1: solo tareas PSSR cerradas. Opción 2: aprobación del TM antes de Start Up.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Medio.</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>C. Workflow</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>¿Los trabajos grandes (por ejemplo, un tanque) van en un MOC por fase o en uno solo?</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Large jobs (e.g. a tank): one MOC per phase or a single MOC?</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Hugo planteó un MOC por fase (vaciado, limpieza, entrada, reparación); Khesar no estuvo de acuerdo. Es una regla de procedimiento; en el sistema se enlazan con Related MOCs.</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>21-oct, Hugo (23:10) y Khesar (23:45).</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>21-oct</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Definirlo en el procedimiento.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Bajo para el sistema.</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>C. Workflow</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>¿Se revisan periódicamente los MOC cerrados (como en Sphera)?</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Periodic review of closed MOCs (as in Sphera)?</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Shaun preguntó por la revisión anual de Sphera; en Intelex, cerrado es definitivo. Hay que confirmar que no se necesita.</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>21-oct, Shaun (35:53).</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>21-oct</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Propuesta: no; los temporales ya tienen fecha de revisión.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Bajo.</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>A. Aprobaciones</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>¿Qué lista de tipos de aprobación necesitamos (funcionales + de nivel)?</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Which approval types do we need (functional + level approvals)?</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Sam quiere conservar los tipos estándar para añadir aprobaciones funcionales; Khesar echa en falta Operaciones. Además hacen falta los tipos de nivel (TM, Regional, Global). Intelex solo trae 6 objetos.</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>21-oct, Sam (8:31) y Khesar (10:07).</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>21-oct</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Lista propuesta: Operations, Maintenance, Engineering, Safety, Environmental + TM, Regional HSEC/Ops, Global HSEC/Ops.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Define la configuración de aprobaciones.</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>Abierta</t>
         </is>
@@ -1973,10 +2466,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Abierta,Decidida,Aplazada,Para Intelex"</formula1>
+    <dataValidation sqref="M2:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Abierta,Parcial,Decidida,Aplazada,Para Intelex"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A,B,C"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/moc/Impala - MoC Workshop Interno 21-oct - Preguntas.xlsx
+++ b/docs/moc/Impala - MoC Workshop Interno 21-oct - Preguntas.xlsx
@@ -180,8 +180,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Preguntas" displayName="Preguntas" ref="A1:M30" headerRowCount="1">
-  <autoFilter ref="A1:M30"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Preguntas" displayName="Preguntas" ref="A1:M33" headerRowCount="1">
+  <autoFilter ref="A1:M33"/>
   <tableColumns count="13">
     <tableColumn id="1" name="#"/>
     <tableColumn id="2" name="Bloque"/>
@@ -499,14 +499,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Workshop interno MoC (21-oct-2026): preguntas abiertas - estado tras la sesión del 21-oct</t>
+          <t>Workshop interno MoC (21-oct-2026): preguntas abiertas - estado tras la sesión del 21-oct y MOC Proposal Rev2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Columnas Respuesta / Estado rellenadas con la transcripción del 21-oct. Preguntas 24-29 = nuevas, surgidas en la sesión.</t>
+          <t>Columnas Respuesta / Estado rellenadas con la transcripción del 21-oct. Preguntas 24-29 = surgidas en la sesión; 30-32 = surgidas de Rev2 de Sam.</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -783,7 +783,7 @@
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>Local = revisión funcional (Operaciones/Mantenimiento) + firma final del TM: nunca una sola persona (Shaun 4:12 y 5:22, Khesar 10:18). Regional y Global = HSEC + Operaciones. La regla exacta va en el mapa por etapa de Sam.</t>
+          <t>Minor = TM + al menos un especialista técnico del terminal (Rev2). Moderate = Regional HSEC + Ops. Major = Global HSEC + Ops.</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Decidida</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Change Impact vinculado a la categoría (tipo de cambio). La matriz incluye el grado de cambio y el de peligro. En revisión del equipo. Stylianos no se trató.</t>
+          <t>Rev2 incluye los cambios de Khesar (Sam alineado). Revisión del equipo en curso; Stylianos sin tratar.</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1104,13 +1104,17 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>No se trató el 21-oct.</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>Rev2: 'Change Type - selection list': un solo tipo por MOC.</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Decidida</t>
         </is>
       </c>
     </row>
@@ -1291,17 +1295,17 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Sigue abierto (Sam 2:36: 'we can come back to that').</t>
+          <t>Rev2: Replacement in Kind pasa a ser 'Simple Change?' (obligatorio). Mismo workflow pero sin checklist de Evaluation/D&amp;A; para cambios de IT u organizativos.</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>Sam / Rodrigo</t>
+          <t>Sam</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Decidida</t>
         </is>
       </c>
     </row>
@@ -1356,13 +1360,17 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>No se trató el 21-oct.</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr"/>
+          <t>Rev2: la emergencia va directa de Initiation a Approval. Regularización a posteriori: sin tratar.</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Parcial</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1490,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Debe ser imposible avanzar sin responder las preguntas (Sam 34:47). Nuevo: las tareas llevan una etapa límite para no bloquear con tareas posteriores.</t>
+          <t>Rev2: 'All items should be answered/completed before progress to next stage is permitted if mandated'. Tasks con 'Pre-Implementation / Pre-Follow Up'.</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1547,7 +1555,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Abierta: ¿checklist estándar o preguntas según el tipo de cambio? El equipo debe pensarlo (Sam 46:10).</t>
+          <t>Rev2: el checklist es un mínimo y se pueden añadir items. Abierto: vincular items a tipo e impacto (p. ej. HAZOP obligatorio en un cambio Major de equipo).</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1557,7 +1565,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Parcial</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2116,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>'Reason for Change &amp; Technical Basis' aceptado (Khesar 37:51). El resto no se trató.</t>
+          <t>'Change Justification' (Rev2, con tooltip). El resto de campos del BRD no están en Rev2: validar.</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2171,11 +2179,19 @@
           <t>Bajo.</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Rev2: se elimina 'Installation Confirmed' (y también 'Start Up Confirmed').</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Decidida</t>
         </is>
       </c>
     </row>
@@ -2228,11 +2244,19 @@
           <t>Medio: campos de Follow Up.</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>Rev2: 'Follow Up Notes' pasa a 'Lessons Learnt'. Preguntas del formulario de auditoría: pendiente.</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Abierta</t>
+          <t>Parcial</t>
         </is>
       </c>
     </row>
@@ -2285,8 +2309,16 @@
           <t>Medio.</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Rev2: se permiten aprobaciones ad hoc en todas las etapas. '¿El TM debe re-aprobar en Implementation / Start Up / Follow Up?': abierto.</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Sam</t>
+        </is>
+      </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
           <t>Abierta</t>
@@ -2464,12 +2496,183 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>B. Clasificación</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Priority se mantiene (Rev2): ¿con qué valores y para qué sirve?</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Priority is kept (Rev2): which values, and what does it drive?</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Rev2 la marca como obligatoria, pero el 21-oct Sam dudó de que dispare algo. Un campo obligatorio que no sirve para nada molesta al usuario.</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Rev2: 'Priority - Mandate, selection list'. 21-oct, Sam (7:26).</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>SAM Rev2</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Opción 1: Low/Medium/High solo informativo. Opción 2: quitar el obligatorio.</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Bajo.</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>C. Workflow</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>¿El PSSR es obligatorio solo para Moderate/Major?</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Is PSSR mandatory only for Moderate / Major changes?</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Rev2 lo deja con interrogante. Define si el campo es obligatorio de forma condicional (lógica simple).</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Rev2: 'PSSR Complete? - Mandated for Moderate/Major only?'.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>SAM Rev2</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Propuesta: obligatorio en Moderate/Major; opcional en Minor.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Medio.</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>C. Workflow</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Simple Change (IT / organizativos): ¿en qué consiste la 'revisión de proceso distinta'?</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Simple Change (IT / Org): what is the 'different process review' they follow?</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Rev2 dice que siguen el mismo workflow sin checklist, pero que tienen 'otra revisión'. Si esa revisión debe quedar en Intelex, hacen falta preguntas o tareas específicas.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Rev2: 'intent is for IT / Org Changes follow different process review'.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>SAM Rev2</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Opción 1: nada en Intelex (se adjunta la evidencia). Opción 2: tareas o checklist corto específico.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Medio.</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>Abierta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="M2:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Abierta,Parcial,Decidida,Aplazada,Para Intelex"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A,B,C"</formula1>
     </dataValidation>
   </dataValidations>
